--- a/Report Test subject/SV00123-ATU-A01/TestCases/API/OSMS-API-Test-Cases.xlsx
+++ b/Report Test subject/SV00123-ATU-A01/TestCases/API/OSMS-API-Test-Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Online-Sales-Management-System\Report Test subject\test-cases\api\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Online-Sales-Management-System\Report Test subject\Powered by GPT\TestCases\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF992C43-D382-412E-A196-6C5176F119A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF782C6-DEB6-4080-8A49-3A8242A1DAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D4903F0-BE73-4DAC-8AAE-21EEC2F57EA8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="153">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -473,13 +473,19 @@
   </si>
   <si>
     <t>JSON response contains categories array and brands array; each entry includes id, name, and productCount.</t>
+  </si>
+  <si>
+    <t>Evidence / Note</t>
+  </si>
+  <si>
+    <t>Primary evidence: TestResults/Evidence/API/newman-full-run.txt ; Secondary artifact: TestResults/RunnerOutput/API/newman-results.xml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -615,8 +621,15 @@
       <family val="2"/>
       <charset val="163"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,6 +807,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -957,8 +976,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1334,60 +1354,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A47BC6F-E786-427D-AB6F-8EA054BF5FBF}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="158.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="174.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="121.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="118.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1436,8 +1478,11 @@
       <c r="P2" t="s">
         <v>30</v>
       </c>
+      <c r="Q2" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1486,8 +1531,11 @@
       <c r="P3" t="s">
         <v>30</v>
       </c>
+      <c r="Q3" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -1536,8 +1584,11 @@
       <c r="P4" t="s">
         <v>30</v>
       </c>
+      <c r="Q4" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -1586,8 +1637,11 @@
       <c r="P5" t="s">
         <v>30</v>
       </c>
+      <c r="Q5" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1636,8 +1690,11 @@
       <c r="P6" t="s">
         <v>30</v>
       </c>
+      <c r="Q6" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1686,8 +1743,11 @@
       <c r="P7" t="s">
         <v>30</v>
       </c>
+      <c r="Q7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -1736,8 +1796,11 @@
       <c r="P8" t="s">
         <v>30</v>
       </c>
+      <c r="Q8" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1786,8 +1849,11 @@
       <c r="P9" t="s">
         <v>30</v>
       </c>
+      <c r="Q9" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -1836,8 +1902,11 @@
       <c r="P10" t="s">
         <v>30</v>
       </c>
+      <c r="Q10" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -1886,8 +1955,11 @@
       <c r="P11" t="s">
         <v>30</v>
       </c>
+      <c r="Q11" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -1936,8 +2008,11 @@
       <c r="P12" t="s">
         <v>30</v>
       </c>
+      <c r="Q12" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -1986,8 +2061,11 @@
       <c r="P13" t="s">
         <v>30</v>
       </c>
+      <c r="Q13" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -2036,8 +2114,11 @@
       <c r="P14" t="s">
         <v>30</v>
       </c>
+      <c r="Q14" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -2086,8 +2167,11 @@
       <c r="P15" t="s">
         <v>30</v>
       </c>
+      <c r="Q15" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>117</v>
       </c>
@@ -2136,8 +2220,11 @@
       <c r="P16" t="s">
         <v>30</v>
       </c>
+      <c r="Q16" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2186,8 +2273,11 @@
       <c r="P17" t="s">
         <v>30</v>
       </c>
+      <c r="Q17" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>132</v>
       </c>
@@ -2236,8 +2326,11 @@
       <c r="P18" t="s">
         <v>30</v>
       </c>
+      <c r="Q18" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>138</v>
       </c>
@@ -2286,8 +2379,11 @@
       <c r="P19" t="s">
         <v>30</v>
       </c>
+      <c r="Q19" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
@@ -2335,6 +2431,9 @@
       </c>
       <c r="P20" t="s">
         <v>30</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
